--- a/reports/pdf_change_20260916.xlsx
+++ b/reports/pdf_change_20260916.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억   ·   현금 29억(0.7%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 2종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -807,7 +807,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,368억   ·   현금 43억(1.3%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,368억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -831,7 +831,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,483억   ·   현금 34억(1.4%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,483억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1029,23 +1029,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1972344000</v>
+        <v>-482344500</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>6.10%→4.84%</t>
+          <t>0.65%→0.46%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>
@@ -1057,30 +1057,30 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-482344500</v>
+        <v>-1972344000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.46%</t>
+          <t>6.10%→4.84%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 17억(0.9%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,929억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1104,7 +1104,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 272억   ·   현금 1억(0.4%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 272억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1128,7 +1128,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 4억(0.9%)      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억      당일 2026-09-16  vs  전영업일 2026-09-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>

--- a/reports/pdf_change_20260916.xlsx
+++ b/reports/pdf_change_20260916.xlsx
@@ -1029,23 +1029,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-482344500</v>
+        <v>-1972344000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.46%</t>
+          <t>6.10%→4.84%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>
@@ -1057,23 +1057,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1972344000</v>
+        <v>-482344500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>6.10%→4.84%</t>
+          <t>0.65%→0.46%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260916.xlsx
+++ b/reports/pdf_change_20260916.xlsx
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 6/7  ·  대기: TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER  ·  검증필요 1건</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1271200000</v>
+        <v>1272470768</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-41</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1375550000</v>
+        <v>-1376925082</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2679000000</v>
+        <v>2681678089</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-16</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-505600000</v>
+        <v>-506105428</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>-12</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-453600000</v>
+        <v>-454053446</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>-5</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-834500000</v>
+        <v>-835334216</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -920,14 +920,16 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>켐트로닉스  (신규)</t>
+          <t>켐트로닉스  (재편입·09/10까지 105주) ※검증필요</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>983512200</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>검증필요</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -948,7 +950,7 @@
         <v>-39</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-3338049000</v>
+        <v>-3342941542</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -971,7 +973,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>5532725000</v>
+        <v>5540834255</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -992,7 +994,7 @@
         <v>-37</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1736099200</v>
+        <v>-1738643782</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1015,7 +1017,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1479735400</v>
+        <v>1481904232</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1036,7 +1038,7 @@
         <v>-15</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1972344000</v>
+        <v>-1975234843</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1064,7 +1066,7 @@
         <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-482344500</v>
+        <v>-483051467</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
